--- a/test-exports/urd-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/urd-2020-01-01-to-2030-01-01.xlsx
@@ -6,17 +6,20 @@
   <sheets>
     <sheet sheetId="1" name="URD purchases" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'URD purchases'!$6:$6</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>URD Purchases - Detailed register</t>
   </si>
   <si>
-    <t>2020-01-01 to 2030-01-01 | 3 purchases</t>
+    <t>01-01-2020 to 01-01-2030 (India Standard Time) | 4 purchases</t>
   </si>
   <si>
     <t>Total purchases</t>
@@ -25,6 +28,9 @@
     <t>Total value</t>
   </si>
   <si>
+    <t>Adjusted in sales</t>
+  </si>
+  <si>
     <t>Total paid</t>
   </si>
   <si>
@@ -64,10 +70,16 @@
     <t>Sale adjustment</t>
   </si>
   <si>
-    <t>Paid</t>
-  </si>
-  <si>
-    <t>Payment</t>
+    <t>Amount payable</t>
+  </si>
+  <si>
+    <t>Amount paid</t>
+  </si>
+  <si>
+    <t>Outstanding</t>
+  </si>
+  <si>
+    <t>Payment method</t>
   </si>
   <si>
     <t>Settled invoice</t>
@@ -79,10 +91,14 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>URD-20260821-29829</t>
-  </si>
-  <si>
-    <t>9423232371</t>
+    <r>
+      <t>URD-20260821-29829</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9423232371</t>
+    </r>
   </si>
   <si>
     <t>Kalyan Abuj</t>
@@ -94,22 +110,28 @@
     <t>22K</t>
   </si>
   <si>
-    <t>CASH</t>
-  </si>
-  <si>
-    <t>URD-20260823-MT5TEA4H-4CE73E04</t>
-  </si>
-  <si>
-    <t>9529138839</t>
+    <t>Cash</t>
+  </si>
+  <si>
+    <r>
+      <t>URD-20260823-MT5TEA4H-4CE73E04</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9529138839</t>
+    </r>
   </si>
   <si>
     <t>BRUCE</t>
   </si>
   <si>
-    <t>MIXED</t>
-  </si>
-  <si>
-    <t>INV-20260823-MT5TDACR-78D3410E</t>
+    <t>Mixed</t>
+  </si>
+  <si>
+    <r>
+      <t>INV-20260823-MT5TDACR-78D3410E</t>
+    </r>
   </si>
   <si>
     <t>URD purchase settled against sale</t>
@@ -118,7 +140,9 @@
     <t>Settled against sale INV-20260823-MT5TDACR-78D3410E</t>
   </si>
   <si>
-    <t>URD-20260828-0001</t>
+    <r>
+      <t>URD-20260828-0001</t>
+    </r>
   </si>
   <si>
     <t>SILVER</t>
@@ -127,20 +151,36 @@
     <t>925</t>
   </si>
   <si>
-    <t>202608280002</t>
+    <r>
+      <t>202608280002</t>
+    </r>
   </si>
   <si>
     <t>Settled against sale 202608280002</t>
+  </si>
+  <si>
+    <r>
+      <t>URD-20260828-0008</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>202608280020</t>
+    </r>
+  </si>
+  <si>
+    <t>Settled against sale 202608280020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="₹#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$₹-en-IN]#,##0.00;[Red]-[$₹-en-IN]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.000;[Red]-0.000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -175,7 +215,7 @@
       <color rgb="FF271A05"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,6 +240,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5A044"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFCF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -227,9 +277,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FFE8E1D8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE8E1D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8E1D8"/>
+      </top>
       <bottom style="thin">
         <color rgb="FFE8E1D8"/>
       </bottom>
@@ -239,34 +295,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -287,8 +361,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A5:P8" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:P8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A6:R10" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A6:R10">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -305,8 +379,10 @@
     <filterColumn colId="13" hiddenButton="1"/>
     <filterColumn colId="14" hiddenButton="1"/>
     <filterColumn colId="15" hiddenButton="1"/>
+    <filterColumn colId="16" hiddenButton="1"/>
+    <filterColumn colId="17" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="16">
+  <tableColumns count="18">
     <tableColumn id="1" name="Purchase date" totalsRowLabel="Total"/>
     <tableColumn id="2" name="URD no." totalsRowFunction="none"/>
     <tableColumn id="3" name="Customer phone" totalsRowFunction="none"/>
@@ -318,13 +394,15 @@
     <tableColumn id="9" name="Rate / g" totalsRowFunction="none"/>
     <tableColumn id="10" name="Total amount" totalsRowFunction="none"/>
     <tableColumn id="11" name="Sale adjustment" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Paid" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Payment" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Settled invoice" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Description" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Notes" totalsRowFunction="none"/>
+    <tableColumn id="12" name="Amount payable" totalsRowFunction="none"/>
+    <tableColumn id="13" name="Amount paid" totalsRowFunction="none"/>
+    <tableColumn id="14" name="Outstanding" totalsRowFunction="none"/>
+    <tableColumn id="15" name="Payment method" totalsRowFunction="none"/>
+    <tableColumn id="16" name="Settled invoice" totalsRowFunction="none"/>
+    <tableColumn id="17" name="Description" totalsRowFunction="none"/>
+    <tableColumn id="18" name="Notes" totalsRowFunction="none"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -653,22 +731,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="8" width="13" customWidth="1"/>
-    <col min="9" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="16" width="30" customWidth="1"/>
+    <col min="9" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="18" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,8 +766,10 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -707,234 +788,349 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="5">
-        <v>2500</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="5">
+        <v>2502</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="5">
+      <c r="J3" s="3"/>
+      <c r="K3" s="5">
+        <v>2402</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="5">
         <v>100</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2400</v>
-      </c>
+      <c r="P3" s="5"/>
     </row>
-    <row r="5" ht="26" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="L6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="O6" s="6" t="s">
         <v>21</v>
       </c>
+      <c r="P6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>46246.75</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+    <row r="7" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>46246.5</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="9">
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="10">
         <v>1.002</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H7" s="10">
         <v>1.002</v>
       </c>
-      <c r="I6" s="10">
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11">
         <v>100</v>
       </c>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11">
         <v>100</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M7" s="11">
+        <v>100</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>46249.5</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="15">
+        <v>2</v>
+      </c>
+      <c r="H8" s="15">
+        <v>2</v>
+      </c>
+      <c r="I8" s="16">
+        <v>200</v>
+      </c>
+      <c r="J8" s="16">
+        <v>400</v>
+      </c>
+      <c r="K8" s="16">
+        <v>400</v>
+      </c>
+      <c r="L8" s="16">
+        <v>0</v>
+      </c>
+      <c r="M8" s="16">
+        <v>0</v>
+      </c>
+      <c r="N8" s="16">
+        <v>0</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>46262.5</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="E9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="10">
+        <v>20</v>
+      </c>
+      <c r="H9" s="10">
+        <v>20</v>
+      </c>
+      <c r="I9" s="11">
+        <v>100</v>
+      </c>
+      <c r="J9" s="11">
+        <v>2000</v>
+      </c>
+      <c r="K9" s="11">
+        <v>2000</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>46249.29170138889</v>
-      </c>
-      <c r="B7" s="8" t="s">
+    <row r="10" ht="32" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>46262.5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="F10" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="G10" s="15">
         <v>2</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H10" s="15">
         <v>2</v>
       </c>
-      <c r="I7" s="10">
-        <v>200</v>
-      </c>
-      <c r="J7" s="10">
-        <v>400</v>
-      </c>
-      <c r="K7" s="10">
-        <v>400</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="8" t="s">
+      <c r="I10" s="16">
+        <v>1</v>
+      </c>
+      <c r="J10" s="16">
+        <v>2</v>
+      </c>
+      <c r="K10" s="16">
+        <v>2</v>
+      </c>
+      <c r="L10" s="16">
+        <v>0</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0</v>
+      </c>
+      <c r="N10" s="16">
+        <v>0</v>
+      </c>
+      <c r="O10" s="14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>46261.82027777778</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="P10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="9">
-        <v>20</v>
-      </c>
-      <c r="H8" s="9">
-        <v>20</v>
-      </c>
-      <c r="I8" s="10">
-        <v>100</v>
-      </c>
-      <c r="J8" s="10">
-        <v>2000</v>
-      </c>
-      <c r="K8" s="10">
-        <v>2000</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>39</v>
+      <c r="R10" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P8"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+  <autoFilter ref="A6:R10"/>
+  <mergeCells count="12">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/test-exports/urd-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/urd-2020-01-01-to-2030-01-01.xlsx
@@ -358,52 +358,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A6:R10" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A6:R10">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-    <filterColumn colId="12" hiddenButton="1"/>
-    <filterColumn colId="13" hiddenButton="1"/>
-    <filterColumn colId="14" hiddenButton="1"/>
-    <filterColumn colId="15" hiddenButton="1"/>
-    <filterColumn colId="16" hiddenButton="1"/>
-    <filterColumn colId="17" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="18">
-    <tableColumn id="1" name="Purchase date" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="URD no." totalsRowFunction="none"/>
-    <tableColumn id="3" name="Customer phone" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Customer" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Metal" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Purity" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Gross wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Net wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Rate / g" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Total amount" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Sale adjustment" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Amount payable" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Amount paid" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Outstanding" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Payment method" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Settled invoice" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Description" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Notes" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1131,8 +1085,5 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>